--- a/stockPicker/fund_flow_top10_history.xlsx
+++ b/stockPicker/fund_flow_top10_history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4206,6 +4206,506 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>002131</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>利欧股份</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>600143</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>金发科技</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>300418</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>昆仑万维</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>002050</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>三花智控</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>4</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>600410</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>华胜天成</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>5</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>002400</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>省广集团</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>6</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>301171</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>易点天下</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>7</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>300063</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>天龙集团</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>8</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>300058</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>蓝色光标</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>9</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>600050</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>中国联通</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>10</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026-01-10 17:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>航天电子</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>岩山科技</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>000901</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>航天科技</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>3</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>300065</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>海兰信</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>4</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>300170</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>汉得信息</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>5</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>600967</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>内蒙一机</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>6</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>600150</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>中国船舶</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>7</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>顺灏股份</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>8</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>300102</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>乾照光电</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>9</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>603019</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>中科曙光</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>10</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:15:03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stockPicker/fund_flow_top10_history.xlsx
+++ b/stockPicker/fund_flow_top10_history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E171"/>
+  <dimension ref="A1:E221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4706,6 +4706,1256 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>航天电子</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>岩山科技</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>000901</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>航天科技</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>300065</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>海兰信</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>4</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>300170</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>汉得信息</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>5</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>600967</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>内蒙一机</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>6</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>600150</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>中国船舶</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>7</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>顺灏股份</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>8</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>300102</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>乾照光电</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>9</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>603019</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>中科曙光</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>10</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>航天电子</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:28:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>岩山科技</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:28:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>000901</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>航天科技</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:28:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>300065</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>海兰信</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>4</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:28:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>300170</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>汉得信息</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>5</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:28:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>600967</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>内蒙一机</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>6</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:28:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>600150</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>中国船舶</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>7</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:28:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>顺灏股份</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>8</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:28:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>300102</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>乾照光电</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>9</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:28:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>603019</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>中科曙光</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>10</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:28:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>航天电子</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>岩山科技</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>000901</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>航天科技</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>3</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>300065</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>海兰信</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>4</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>300170</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>汉得信息</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>5</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>600967</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>内蒙一机</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>6</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>600150</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>中国船舶</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>7</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>顺灏股份</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>8</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>300102</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>乾照光电</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>9</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>603019</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>中科曙光</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>10</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:30:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>航天电子</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>岩山科技</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>000901</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>航天科技</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>3</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>300065</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>海兰信</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>4</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>300170</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>汉得信息</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>5</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>600967</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>内蒙一机</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>6</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>600150</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>中国船舶</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>7</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>顺灏股份</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>8</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>300102</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>乾照光电</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>9</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>603019</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>中科曙光</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>10</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>航天电子</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>岩山科技</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>2</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>000901</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>航天科技</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>3</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>300065</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>海兰信</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>4</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>300170</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>汉得信息</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>5</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>600967</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>内蒙一机</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>6</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>600150</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>中国船舶</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>7</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>002565</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>顺灏股份</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>8</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>300102</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>乾照光电</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>9</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>603019</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>中科曙光</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>10</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2026-01-11 16:41:14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stockPicker/fund_flow_top10_history.xlsx
+++ b/stockPicker/fund_flow_top10_history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:E341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5956,6 +5956,3006 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>002600</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>领益智造</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>2</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>600118</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>中国卫星</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>3</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>山子高科</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>4</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>岩山科技</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>5</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>601099</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>太平洋</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>6</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>002465</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>海格通信</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>7</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>600839</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>四川长虹</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>8</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>北方稀土</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>9</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>000066</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>中国长城</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>10</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>2026-01-12 11:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>002600</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>领益智造</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>2</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>600118</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>中国卫星</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>3</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>山子高科</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>4</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>岩山科技</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>5</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>601099</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>太平洋</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>6</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>002465</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>海格通信</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>7</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>600839</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>四川长虹</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>8</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>北方稀土</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>9</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>000066</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>中国长城</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>10</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>2026-01-12 12:10:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>山子高科</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>1</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>岩山科技</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>航天电子</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>3</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>300773</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>拉卡拉</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>4</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>002463</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>沪电股份</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>5</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>6</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>603000</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>人民网</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>7</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>601216</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>君正集团</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>8</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>000725</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>京东方Ａ</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>9</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>002354</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>天娱数科</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>10</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>000981</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>山子高科</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>002195</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>岩山科技</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>600879</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>航天电子</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>3</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>300773</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>拉卡拉</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>4</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>002463</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>沪电股份</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>5</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>300059</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>6</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>603000</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>人民网</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>7</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>601216</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>君正集团</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>8</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>000725</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>京东方Ａ</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>9</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>002354</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>天娱数科</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>10</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>2026-01-13 21:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>689009</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>九号公司-WD</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>688981</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>2</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>688819</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>天能股份</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>3</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>688809</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>强一股份</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>4</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>688807</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>优迅股份</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>5</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>688805</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>健信超导</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>6</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>688802</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>沐曦股份-U</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>7</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>688800</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>瑞可达</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>8</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>688799</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>华纳药厂</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>9</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>688798</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>艾为电子</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>10</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>689009</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>九号公司-WD</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>688981</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>688819</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>天能股份</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>3</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>688809</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>强一股份</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>4</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>688807</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>优迅股份</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>5</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>688805</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>健信超导</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>6</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>688802</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>沐曦股份-U</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>7</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>688800</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>瑞可达</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>8</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>688799</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>华纳药厂</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>9</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>688798</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>艾为电子</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>10</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>2026-01-14 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>002475</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>立讯精密</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>1</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>2</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>002130</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>沃尔核材</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>3</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>4</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>5</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>600151</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>航天机电</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>6</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>301308</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>江波龙</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>7</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>603352</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>N至信</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>8</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>603799</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>华友钴业</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>9</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>002463</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>沪电股份</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>10</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>002475</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>立讯精密</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>1</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>002130</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>沃尔核材</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>3</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>4</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>5</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>600151</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>航天机电</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>6</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>301308</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>江波龙</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>7</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>603352</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>N至信</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>8</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>603799</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>华友钴业</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>9</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>002463</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>沪电股份</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>10</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>2026-01-15 09:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>002475</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>立讯精密</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>1</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>2</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>002130</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>沃尔核材</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>3</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>4</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>5</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>600151</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>航天机电</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>6</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>301308</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>江波龙</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>7</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>603352</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>N至信</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>8</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>603799</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>华友钴业</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>9</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>002463</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>沪电股份</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>10</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2026-01-15 23:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>601138</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>XD工业富</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>1</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>603986</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>兆易创新</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>2</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>600584</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>长电科技</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>3</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>002050</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>三花智控</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>4</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>5</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>600703</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>三安光电</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>6</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>601669</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>中国电建</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>7</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>000559</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>万向钱潮</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>8</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>300274</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>阳光电源</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>9</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>603667</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>五洲新春</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>10</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>601138</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>XD工业富</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>1</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:34:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>603986</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>兆易创新</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>2</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:34:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>600584</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>长电科技</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>3</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:34:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>002050</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>三花智控</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>4</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:34:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>5</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:34:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>600703</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>三安光电</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>6</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:34:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>601669</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>中国电建</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>7</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:34:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>000559</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>万向钱潮</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>8</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:34:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>300274</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>阳光电源</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>9</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:34:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>603667</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>五洲新春</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>10</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>2026-01-16 17:34:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>600089</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>特变电工</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>1</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:37:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>中国西电</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>2</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:37:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>3</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:37:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>4</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:37:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>601888</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>中国中免</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>5</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:37:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>002202</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>金风科技</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>6</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:37:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>300274</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>阳光电源</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>7</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:37:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>600372</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>中航机载</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>8</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:37:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>300444</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>双杰电气</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>9</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:37:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>601689</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>拓普集团</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>10</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>2026-01-19 19:37:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
